--- a/Blackwood_CFS_Master_Inventory_with_34P_and_CAFS24_Rescue_Unchanged.xlsx
+++ b/Blackwood_CFS_Master_Inventory_with_34P_and_CAFS24_Rescue_Unchanged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\Blackwood CFS\App creation\V2 stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E91566A-ABB7-486C-8DC6-667CF80EDEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBB854D-21A9-4AFF-A790-3ABB95C5C19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2410" uniqueCount="918">
   <si>
     <t>Item_ID</t>
   </si>
@@ -751,12 +751,6 @@
     <t>Cabin</t>
   </si>
   <si>
-    <t>Front Seat</t>
-  </si>
-  <si>
-    <t>Above Driver + Console</t>
-  </si>
-  <si>
     <t>DRIVERS LOG BOOK</t>
   </si>
   <si>
@@ -872,9 +866,6 @@
   </si>
   <si>
     <t>BR-0155</t>
-  </si>
-  <si>
-    <t>PENCIL CASE containing</t>
   </si>
   <si>
     <t>Chinagraph pencil
@@ -1300,9 +1291,6 @@
   </si>
   <si>
     <t>34P-0018</t>
-  </si>
-  <si>
-    <t>POUCH containing</t>
   </si>
   <si>
     <t>34P-0024</t>
@@ -6271,13 +6259,11 @@
         <v>230</v>
       </c>
       <c r="D103" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>233</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -6294,7 +6280,7 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>10</v>
@@ -6303,13 +6289,11 @@
         <v>230</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -6326,7 +6310,7 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>10</v>
@@ -6335,13 +6319,11 @@
         <v>230</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -6358,7 +6340,7 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>10</v>
@@ -6367,13 +6349,11 @@
         <v>230</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -6390,7 +6370,7 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>10</v>
@@ -6399,13 +6379,11 @@
         <v>230</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -6422,7 +6400,7 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>10</v>
@@ -6431,13 +6409,11 @@
         <v>230</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -6454,7 +6430,7 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
@@ -6463,13 +6439,11 @@
         <v>230</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -6486,7 +6460,7 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>10</v>
@@ -6495,13 +6469,11 @@
         <v>230</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
@@ -6518,7 +6490,7 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>10</v>
@@ -6527,13 +6499,11 @@
         <v>230</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
@@ -6550,7 +6520,7 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>10</v>
@@ -6559,13 +6529,11 @@
         <v>230</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
@@ -6582,7 +6550,7 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>10</v>
@@ -6591,13 +6559,11 @@
         <v>230</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -6614,7 +6580,7 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>10</v>
@@ -6623,13 +6589,11 @@
         <v>230</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -6646,7 +6610,7 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>10</v>
@@ -6655,13 +6619,11 @@
         <v>230</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -6678,7 +6640,7 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>10</v>
@@ -6687,13 +6649,11 @@
         <v>230</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -6710,7 +6670,7 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>10</v>
@@ -6719,13 +6679,11 @@
         <v>230</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -6742,7 +6700,7 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>10</v>
@@ -6751,13 +6709,11 @@
         <v>230</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -6774,7 +6730,7 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>10</v>
@@ -6783,13 +6739,11 @@
         <v>230</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -6806,7 +6760,7 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>10</v>
@@ -6815,13 +6769,11 @@
         <v>230</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
@@ -6838,7 +6790,7 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>10</v>
@@ -6847,13 +6799,11 @@
         <v>230</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
@@ -6870,7 +6820,7 @@
     </row>
     <row r="122" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>10</v>
@@ -6879,18 +6829,16 @@
         <v>230</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>255</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>272</v>
+        <v>882</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>13</v>
@@ -6904,7 +6852,7 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>10</v>
@@ -6913,13 +6861,11 @@
         <v>230</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
@@ -6936,7 +6882,7 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>10</v>
@@ -6945,13 +6891,11 @@
         <v>230</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E124" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
@@ -6968,7 +6912,7 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>10</v>
@@ -6977,13 +6921,11 @@
         <v>230</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -7000,7 +6942,7 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>10</v>
@@ -7009,13 +6951,11 @@
         <v>230</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -7032,7 +6972,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>10</v>
@@ -7041,13 +6981,11 @@
         <v>230</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -7064,7 +7002,7 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>10</v>
@@ -7073,13 +7011,11 @@
         <v>230</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
@@ -7096,7 +7032,7 @@
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>10</v>
@@ -7105,13 +7041,11 @@
         <v>230</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
@@ -7128,7 +7062,7 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>10</v>
@@ -7137,13 +7071,11 @@
         <v>230</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
@@ -7160,7 +7092,7 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>10</v>
@@ -7169,13 +7101,11 @@
         <v>230</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -7192,7 +7122,7 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>10</v>
@@ -7201,13 +7131,11 @@
         <v>230</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -7224,7 +7152,7 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>10</v>
@@ -7233,13 +7161,11 @@
         <v>230</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
@@ -7256,7 +7182,7 @@
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>10</v>
@@ -7265,11 +7191,11 @@
         <v>230</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -7286,7 +7212,7 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>10</v>
@@ -7295,11 +7221,11 @@
         <v>230</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -7316,7 +7242,7 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>10</v>
@@ -7325,11 +7251,11 @@
         <v>230</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -7346,7 +7272,7 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>10</v>
@@ -7355,11 +7281,11 @@
         <v>230</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -7376,7 +7302,7 @@
     </row>
     <row r="138" spans="1:16" ht="103.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
@@ -7385,16 +7311,16 @@
         <v>230</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
       <c r="I138" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J138" s="5" t="s">
         <v>13</v>
@@ -7408,7 +7334,7 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>10</v>
@@ -7417,13 +7343,11 @@
         <v>230</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -7440,7 +7364,7 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>10</v>
@@ -7449,13 +7373,11 @@
         <v>230</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E140" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E140" s="5"/>
+      <c r="F140" s="5" t="s">
         <v>306</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>309</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -7472,7 +7394,7 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>10</v>
@@ -7481,13 +7403,11 @@
         <v>230</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E141" s="5"/>
       <c r="F141" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -7504,7 +7424,7 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
@@ -7513,13 +7433,11 @@
         <v>230</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E142" s="5"/>
       <c r="F142" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7536,7 +7454,7 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
@@ -7545,13 +7463,11 @@
         <v>230</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -7568,7 +7484,7 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
@@ -7577,13 +7493,11 @@
         <v>230</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -7600,7 +7514,7 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -7609,13 +7523,11 @@
         <v>230</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -7632,7 +7544,7 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>10</v>
@@ -7641,13 +7553,11 @@
         <v>230</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>306</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E146" s="5"/>
       <c r="F146" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -7682,20 +7592,20 @@
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
@@ -7706,20 +7616,20 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
@@ -7730,20 +7640,20 @@
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -7754,20 +7664,20 @@
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -7778,20 +7688,20 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -7802,20 +7712,20 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E153" s="6"/>
       <c r="F153" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -7826,20 +7736,20 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -7850,20 +7760,20 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -7874,20 +7784,20 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -7898,20 +7808,20 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -7922,20 +7832,20 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -7946,20 +7856,20 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -7970,20 +7880,20 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -7994,20 +7904,20 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -8018,20 +7928,20 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8042,20 +7952,20 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8066,20 +7976,20 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8090,25 +8000,25 @@
     </row>
     <row r="165" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
       <c r="I165" s="6" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="J165" s="6" t="s">
         <v>13</v>
@@ -8176,25 +8086,25 @@
     </row>
     <row r="171" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E171" s="6"/>
       <c r="F171" s="6" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="6" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="J171" s="6" t="s">
         <v>13</v>
@@ -8262,20 +8172,20 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E177" s="6"/>
       <c r="F177" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
@@ -8286,20 +8196,20 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E178" s="6"/>
       <c r="F178" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
@@ -8310,20 +8220,20 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
@@ -8334,20 +8244,20 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
@@ -8358,24 +8268,24 @@
     </row>
     <row r="181" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
       <c r="I181" s="6" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="J181" s="6" t="s">
         <v>13</v>
@@ -8443,20 +8353,20 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E187" s="6"/>
       <c r="F187" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
@@ -8467,20 +8377,20 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
@@ -8491,20 +8401,20 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
@@ -8515,20 +8425,20 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
@@ -8539,20 +8449,20 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
@@ -8563,20 +8473,20 @@
     </row>
     <row r="192" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
@@ -8587,20 +8497,20 @@
     </row>
     <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E193" s="6"/>
       <c r="F193" s="6" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
@@ -8611,20 +8521,20 @@
     </row>
     <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E194" s="6"/>
       <c r="F194" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
@@ -8635,20 +8545,20 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E195" s="6"/>
       <c r="F195" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
@@ -8659,20 +8569,20 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
@@ -8683,20 +8593,20 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E197" s="6"/>
       <c r="F197" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
@@ -8707,20 +8617,20 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E198" s="6"/>
       <c r="F198" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
@@ -8731,20 +8641,20 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E199" s="6"/>
       <c r="F199" s="6" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -8755,20 +8665,20 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -8779,20 +8689,20 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
@@ -8803,20 +8713,20 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E202" s="6"/>
       <c r="F202" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -8827,20 +8737,20 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E203" s="6"/>
       <c r="F203" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -8851,20 +8761,20 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E204" s="6"/>
       <c r="F204" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -8875,20 +8785,20 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E205" s="6"/>
       <c r="F205" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
@@ -8899,23 +8809,23 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
       <c r="F206" s="6" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
       <c r="I206" s="6" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="J206" s="6" t="s">
         <v>13</v>
@@ -8923,18 +8833,18 @@
     </row>
     <row r="207" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
@@ -8945,18 +8855,18 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
@@ -8967,18 +8877,18 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
@@ -8989,18 +8899,18 @@
     </row>
     <row r="210" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
@@ -9011,18 +8921,18 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
@@ -9033,22 +8943,22 @@
     </row>
     <row r="212" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D212" s="6"/>
       <c r="F212" s="6" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
       <c r="I212" s="6" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="J212" s="6" t="s">
         <v>13</v>
@@ -9152,18 +9062,18 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
       <c r="F221" s="6" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
@@ -9174,18 +9084,18 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
@@ -9196,18 +9106,18 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
@@ -9218,18 +9128,18 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
@@ -9240,18 +9150,18 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
@@ -9262,18 +9172,18 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
@@ -9284,18 +9194,18 @@
     </row>
     <row r="227" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
@@ -9306,18 +9216,18 @@
     </row>
     <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
@@ -9328,18 +9238,18 @@
     </row>
     <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
@@ -9350,18 +9260,18 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
@@ -9372,18 +9282,18 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
@@ -9394,18 +9304,18 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
@@ -9416,18 +9326,18 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
@@ -9438,18 +9348,18 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
@@ -9460,18 +9370,18 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
@@ -9482,18 +9392,18 @@
     </row>
     <row r="236" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
@@ -9504,18 +9414,18 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -9526,18 +9436,18 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
@@ -9548,18 +9458,18 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
@@ -9570,18 +9480,18 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
@@ -9592,18 +9502,18 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
@@ -9614,23 +9524,23 @@
     </row>
     <row r="242" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="J242" s="6" t="s">
         <v>13</v>
@@ -9710,18 +9620,18 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
@@ -9732,22 +9642,22 @@
     </row>
     <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D250" s="6"/>
       <c r="F250" s="6" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
       <c r="I250" s="6" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="J250" s="6" t="s">
         <v>13</v>
@@ -9767,18 +9677,18 @@
     </row>
     <row r="252" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
       <c r="F252" s="6" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
@@ -9789,18 +9699,18 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="6" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
       <c r="F253" s="6" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
@@ -9811,18 +9721,18 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
       <c r="F254" s="6" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
@@ -9833,18 +9743,18 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
@@ -9855,18 +9765,18 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
@@ -9877,18 +9787,18 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
@@ -9899,18 +9809,18 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
@@ -9921,18 +9831,18 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
@@ -9943,18 +9853,18 @@
     </row>
     <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
@@ -9965,18 +9875,18 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9987,18 +9897,18 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -10009,18 +9919,18 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
@@ -10031,18 +9941,18 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
@@ -10053,13 +9963,13 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
@@ -10075,18 +9985,18 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
@@ -10097,18 +10007,18 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10119,18 +10029,18 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10141,18 +10051,18 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10163,18 +10073,18 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10185,18 +10095,18 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10207,22 +10117,22 @@
     </row>
     <row r="272" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
       <c r="I272" s="6" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="J272" s="6" t="s">
         <v>13</v>
@@ -10290,23 +10200,23 @@
     </row>
     <row r="278" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
       <c r="I278" s="6" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="J278" s="6" t="s">
         <v>13</v>
@@ -10638,18 +10548,18 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="6" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D306" s="6"/>
       <c r="E306" s="6"/>
       <c r="F306" s="6" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="G306" s="6"/>
       <c r="H306" s="6"/>
@@ -10660,13 +10570,13 @@
     </row>
     <row r="307" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A307" s="6" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D307" s="6"/>
       <c r="E307" s="6"/>
@@ -10682,18 +10592,18 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="6" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D308" s="6"/>
       <c r="E308" s="6"/>
       <c r="F308" s="6" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G308" s="6"/>
       <c r="H308" s="6"/>
@@ -10704,18 +10614,18 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="6" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D309" s="6"/>
       <c r="E309" s="6"/>
       <c r="F309" s="6" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G309" s="6"/>
       <c r="H309" s="6"/>
@@ -10726,18 +10636,18 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="6" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D310" s="6"/>
       <c r="E310" s="6"/>
       <c r="F310" s="6" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G310" s="6"/>
       <c r="H310" s="6"/>
@@ -10748,18 +10658,18 @@
     </row>
     <row r="311" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A311" s="6" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D311" s="6"/>
       <c r="E311" s="6"/>
       <c r="F311" s="6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="G311" s="6"/>
       <c r="H311" s="6"/>
@@ -10770,18 +10680,18 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D312" s="6"/>
       <c r="E312" s="6"/>
       <c r="F312" s="6" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G312" s="6"/>
       <c r="H312" s="6"/>
@@ -10792,22 +10702,22 @@
     </row>
     <row r="313" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A313" s="6" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D313" s="6"/>
       <c r="F313" s="6" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G313" s="6"/>
       <c r="H313" s="6"/>
       <c r="I313" s="6" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="J313" s="6" t="s">
         <v>13</v>
@@ -10851,18 +10761,18 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="6" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D317" s="6"/>
       <c r="E317" s="6"/>
       <c r="F317" s="6" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G317" s="6"/>
       <c r="H317" s="6"/>
@@ -10873,18 +10783,18 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="6" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D318" s="6"/>
       <c r="E318" s="6"/>
       <c r="F318" s="6" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G318" s="6"/>
       <c r="H318" s="6"/>
@@ -10895,18 +10805,18 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D319" s="6"/>
       <c r="E319" s="6"/>
       <c r="F319" s="6" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G319" s="6"/>
       <c r="H319" s="6"/>
@@ -10917,18 +10827,18 @@
     </row>
     <row r="320" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A320" s="6" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D320" s="6"/>
       <c r="E320" s="6"/>
       <c r="F320" s="6" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G320" s="6"/>
       <c r="H320" s="6"/>
@@ -10939,18 +10849,18 @@
     </row>
     <row r="321" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A321" s="6" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D321" s="6"/>
       <c r="E321" s="6"/>
       <c r="F321" s="6" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G321" s="6"/>
       <c r="H321" s="6"/>
@@ -10961,18 +10871,18 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="6" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D322" s="6"/>
       <c r="E322" s="6"/>
       <c r="F322" s="6" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G322" s="6"/>
       <c r="H322" s="6"/>
@@ -10983,18 +10893,18 @@
     </row>
     <row r="323" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A323" s="6" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D323" s="6"/>
       <c r="E323" s="6"/>
       <c r="F323" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G323" s="6"/>
       <c r="H323" s="6"/>
@@ -11005,18 +10915,18 @@
     </row>
     <row r="324" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A324" s="6" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D324" s="6"/>
       <c r="E324" s="6"/>
       <c r="F324" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="G324" s="6"/>
       <c r="H324" s="6"/>
@@ -11027,18 +10937,18 @@
     </row>
     <row r="325" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A325" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D325" s="6"/>
       <c r="E325" s="6"/>
       <c r="F325" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G325" s="6"/>
       <c r="H325" s="6"/>
@@ -11049,18 +10959,18 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="6" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D326" s="6"/>
       <c r="E326" s="6"/>
       <c r="F326" s="6" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="G326" s="6"/>
       <c r="H326" s="6"/>
@@ -11071,18 +10981,18 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="6" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D327" s="6"/>
       <c r="E327" s="6"/>
       <c r="F327" s="6" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="G327" s="6"/>
       <c r="H327" s="6"/>
@@ -11093,18 +11003,18 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="6" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D328" s="6"/>
       <c r="E328" s="6"/>
       <c r="F328" s="6" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G328" s="6"/>
       <c r="H328" s="6"/>
@@ -11115,18 +11025,18 @@
     </row>
     <row r="329" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A329" s="6" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
       <c r="F329" s="6" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="G329" s="6"/>
       <c r="H329" s="6"/>
@@ -11137,18 +11047,18 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="6" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
       <c r="F330" s="6" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
@@ -11159,18 +11069,18 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
       <c r="F331" s="6" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
@@ -11181,18 +11091,18 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
       <c r="F332" s="6" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
@@ -11203,18 +11113,18 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
       <c r="F333" s="6" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
@@ -11225,18 +11135,18 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
       <c r="F334" s="6" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
@@ -11247,18 +11157,18 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
       <c r="F335" s="6" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
@@ -11269,18 +11179,18 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
       <c r="F336" s="6" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
@@ -11291,18 +11201,18 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
       <c r="F337" s="6" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
@@ -11313,18 +11223,18 @@
     </row>
     <row r="338" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
       <c r="F338" s="6" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
@@ -11335,18 +11245,18 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
       <c r="F339" s="6" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
@@ -11357,18 +11267,18 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
       <c r="F340" s="6" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
@@ -11379,13 +11289,13 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
@@ -11401,18 +11311,18 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11423,18 +11333,18 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11445,18 +11355,18 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11467,18 +11377,18 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11489,18 +11399,18 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11511,18 +11421,18 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11533,18 +11443,18 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11555,18 +11465,18 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11577,18 +11487,18 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11599,18 +11509,18 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11621,18 +11531,18 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11643,18 +11553,18 @@
     </row>
     <row r="353" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11665,18 +11575,18 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11699,20 +11609,20 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="6" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C356" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D356" s="6" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E356" s="6"/>
       <c r="F356" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G356" s="6"/>
       <c r="H356" s="6"/>
@@ -11723,20 +11633,20 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="6" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C357" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D357" s="6" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E357" s="6"/>
       <c r="F357" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G357" s="6"/>
       <c r="H357" s="6"/>
@@ -11747,20 +11657,20 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C358" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D358" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11771,25 +11681,25 @@
     </row>
     <row r="359" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C359" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D359" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E359" s="6"/>
       <c r="F359" s="11" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
       <c r="I359" s="11" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="J359" s="6" t="s">
         <v>13</v>
@@ -11857,20 +11767,20 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="6" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C365" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D365" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E365" s="6"/>
       <c r="F365" s="6" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
@@ -11881,20 +11791,20 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C366" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D366" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E366" s="6"/>
       <c r="F366" s="6" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
@@ -11905,20 +11815,20 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C367" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D367" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E367" s="6"/>
       <c r="F367" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
@@ -11929,20 +11839,20 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C368" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D368" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11953,20 +11863,20 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C369" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D369" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11977,20 +11887,20 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C370" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D370" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -12001,20 +11911,20 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C371" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D371" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E371" s="6"/>
       <c r="F371" s="6" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
@@ -12025,20 +11935,20 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C372" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D372" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E372" s="6"/>
       <c r="F372" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
@@ -12049,20 +11959,20 @@
     </row>
     <row r="373" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C373" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D373" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E373" s="6"/>
       <c r="F373" s="6" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
@@ -12073,20 +11983,20 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C374" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D374" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E374" s="6"/>
       <c r="F374" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
@@ -12097,20 +12007,20 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C375" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D375" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
@@ -12121,20 +12031,20 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C376" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D376" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E376" s="6"/>
       <c r="F376" s="6" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
@@ -12145,20 +12055,20 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C377" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D377" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12169,20 +12079,20 @@
     </row>
     <row r="379" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="11" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C379" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D379" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E379" s="6"/>
       <c r="F379" s="11" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="G379" s="6"/>
       <c r="H379" s="6"/>
@@ -12193,27 +12103,25 @@
     </row>
     <row r="380" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A380" s="6" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C380" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D380" s="11" t="s">
-        <v>885</v>
-      </c>
-      <c r="E380" s="6" t="s">
-        <v>408</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="E380" s="6"/>
       <c r="F380" s="11" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
       <c r="I380" s="11" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="J380" s="6" t="s">
         <v>13</v>
@@ -12257,27 +12165,25 @@
     </row>
     <row r="384" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A384" s="6" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C384" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D384" s="6" t="s">
-        <v>687</v>
-      </c>
-      <c r="E384" s="6" t="s">
-        <v>272</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="E384" s="6"/>
       <c r="F384" s="11" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
       <c r="I384" s="11" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="J384" s="6" t="s">
         <v>13</v>
@@ -12369,27 +12275,25 @@
     </row>
     <row r="392" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A392" s="6" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C392" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D392" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E392" s="6" t="s">
-        <v>691</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="E392" s="6"/>
       <c r="F392" s="6" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
       <c r="I392" s="11" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="J392" s="6" t="s">
         <v>13</v>
@@ -12457,20 +12361,20 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="6" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C398" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D398" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E398" s="6"/>
       <c r="F398" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G398" s="6"/>
       <c r="H398" s="6"/>
@@ -12481,20 +12385,20 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="6" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C399" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D399" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E399" s="6"/>
       <c r="F399" s="6" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
@@ -12505,20 +12409,20 @@
     </row>
     <row r="400" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="6" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C400" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D400" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
@@ -12529,20 +12433,20 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C401" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D401" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -12553,20 +12457,20 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C402" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D402" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E402" s="6"/>
       <c r="F402" s="6" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
@@ -12577,20 +12481,20 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C403" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D403" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E403" s="6"/>
       <c r="F403" s="6" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
@@ -12601,20 +12505,20 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C404" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D404" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
@@ -12625,20 +12529,20 @@
     </row>
     <row r="405" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C405" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D405" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
@@ -12649,20 +12553,20 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B406" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C406" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D406" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E406" s="6"/>
       <c r="F406" s="6" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
@@ -12673,20 +12577,20 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C407" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D407" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E407" s="6"/>
       <c r="F407" s="6" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
@@ -12697,20 +12601,20 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C408" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E408" s="6"/>
       <c r="F408" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
@@ -12721,20 +12625,20 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C409" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D409" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E409" s="6"/>
       <c r="F409" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
@@ -12745,20 +12649,20 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C410" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E410" s="6"/>
       <c r="F410" s="11" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12769,20 +12673,20 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C411" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D411" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E411" s="6"/>
       <c r="F411" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -12793,20 +12697,20 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C412" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D412" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E412" s="6"/>
       <c r="F412" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -12817,20 +12721,20 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C413" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D413" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E413" s="6"/>
       <c r="F413" s="11" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12841,20 +12745,20 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C414" s="6" t="s">
         <v>230</v>
       </c>
       <c r="D414" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E414" s="6"/>
       <c r="F414" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
@@ -12865,18 +12769,18 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C415" s="11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D415" s="6"/>
       <c r="E415" s="6"/>
       <c r="F415" s="6" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
@@ -12887,18 +12791,18 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="6" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C416" s="11" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D416" s="6"/>
       <c r="E416" s="6"/>
       <c r="F416" s="6" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G416" s="6"/>
       <c r="H416" s="6"/>
@@ -12909,18 +12813,18 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="6" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C417" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D417" s="6"/>
       <c r="E417" s="6"/>
       <c r="F417" s="6" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G417" s="6"/>
       <c r="H417" s="6"/>
@@ -12931,18 +12835,18 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="6" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B418" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C418" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D418" s="6"/>
       <c r="E418" s="6"/>
       <c r="F418" s="6" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G418" s="6"/>
       <c r="H418" s="6"/>
@@ -12953,13 +12857,13 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C419" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D419" s="6"/>
       <c r="E419" s="6"/>
@@ -12975,13 +12879,13 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C420" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
@@ -12997,18 +12901,18 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C421" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
       <c r="F421" s="11" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -13019,13 +12923,13 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C422" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
@@ -13041,18 +12945,18 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C423" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -13063,18 +12967,18 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C424" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -13085,18 +12989,18 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C425" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
       <c r="F425" s="6" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13107,18 +13011,18 @@
     </row>
     <row r="426" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C426" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13129,18 +13033,18 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C427" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
       <c r="F427" s="6" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -13151,18 +13055,18 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
       <c r="F428" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
@@ -13173,18 +13077,18 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
       <c r="F429" s="6" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
@@ -13195,18 +13099,18 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
       <c r="F430" s="6" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
@@ -13217,18 +13121,18 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
@@ -13239,18 +13143,18 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
       <c r="F432" s="6" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
@@ -13261,18 +13165,18 @@
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="6" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D433" s="6"/>
       <c r="E433" s="6"/>
       <c r="F433" s="6" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="G433" s="6"/>
       <c r="H433" s="6"/>
@@ -13283,18 +13187,18 @@
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="6" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B434" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D434" s="6"/>
       <c r="E434" s="6"/>
       <c r="F434" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="G434" s="6"/>
       <c r="H434" s="6"/>
@@ -13305,18 +13209,18 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="6" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D435" s="6"/>
       <c r="E435" s="6"/>
       <c r="F435" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G435" s="6"/>
       <c r="H435" s="6"/>
@@ -13327,18 +13231,18 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="6" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D436" s="6"/>
       <c r="E436" s="6"/>
       <c r="F436" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G436" s="6"/>
       <c r="H436" s="6"/>
@@ -13349,18 +13253,18 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="6" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D437" s="6"/>
       <c r="E437" s="6"/>
       <c r="F437" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="G437" s="6"/>
       <c r="H437" s="6"/>
@@ -13371,18 +13275,18 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
@@ -13393,18 +13297,18 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B439" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13415,18 +13319,18 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
@@ -13437,18 +13341,18 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B441" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
@@ -13459,18 +13363,18 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13481,18 +13385,18 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
@@ -13503,23 +13407,23 @@
     </row>
     <row r="444" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C444" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
       <c r="F444" s="11" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
       <c r="I444" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="J444" s="6" t="s">
         <v>13</v>
@@ -13779,18 +13683,18 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B466" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
       <c r="F466" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
@@ -13801,18 +13705,18 @@
     </row>
     <row r="467" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B467" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C467" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13823,18 +13727,18 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B468" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13845,18 +13749,18 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B469" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C469" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13867,23 +13771,23 @@
     </row>
     <row r="470" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B470" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C470" s="11" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="11" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
       <c r="I470" s="11" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="J470" s="6" t="s">
         <v>13</v>
@@ -14143,23 +14047,23 @@
     </row>
     <row r="492" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A492" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B492" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C492" s="11" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D492" s="6"/>
       <c r="E492" s="6"/>
       <c r="F492" s="11" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="G492" s="6"/>
       <c r="H492" s="6"/>
       <c r="I492" s="11" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="J492" s="6" t="s">
         <v>13</v>
@@ -14263,18 +14167,18 @@
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" s="6" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B501" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D501" s="6"/>
       <c r="E501" s="6"/>
       <c r="F501" s="6" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="G501" s="6"/>
       <c r="H501" s="6"/>
@@ -14285,13 +14189,13 @@
     </row>
     <row r="502" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A502" s="6" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B502" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D502" s="6"/>
       <c r="E502" s="6"/>
@@ -14307,18 +14211,18 @@
     </row>
     <row r="503" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A503" s="6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B503" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D503" s="6"/>
       <c r="E503" s="6"/>
       <c r="F503" s="6" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="G503" s="6"/>
       <c r="H503" s="6"/>
@@ -14329,13 +14233,13 @@
     </row>
     <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" s="6" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B504" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D504" s="6"/>
       <c r="E504" s="6"/>
@@ -14351,18 +14255,18 @@
     </row>
     <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" s="6" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B505" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D505" s="6"/>
       <c r="E505" s="6"/>
       <c r="F505" s="6" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="G505" s="6"/>
       <c r="H505" s="6"/>
@@ -14373,18 +14277,18 @@
     </row>
     <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" s="6" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B506" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D506" s="6"/>
       <c r="E506" s="6"/>
       <c r="F506" s="6" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="G506" s="6"/>
       <c r="H506" s="6"/>
@@ -14395,23 +14299,23 @@
     </row>
     <row r="507" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A507" s="6" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B507" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D507" s="6"/>
       <c r="E507" s="6"/>
       <c r="F507" s="11" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G507" s="6"/>
       <c r="H507" s="6"/>
       <c r="I507" s="11" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="J507" s="6" t="s">
         <v>13</v>
@@ -14431,18 +14335,18 @@
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" s="6" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B509" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D509" s="6"/>
       <c r="E509" s="6"/>
       <c r="F509" s="6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="G509" s="6"/>
       <c r="H509" s="6"/>
@@ -14453,23 +14357,23 @@
     </row>
     <row r="510" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A510" s="6" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B510" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
       <c r="F510" s="6" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
       <c r="I510" s="11" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="J510" s="6" t="s">
         <v>13</v>
@@ -14525,13 +14429,13 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="6" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B515" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C515" s="11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D515" s="6"/>
       <c r="E515" s="6"/>
@@ -14547,18 +14451,18 @@
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="6" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B516" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C516" s="11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D516" s="6"/>
       <c r="E516" s="6"/>
       <c r="F516" s="6" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G516" s="6"/>
       <c r="H516" s="6"/>
@@ -14569,18 +14473,18 @@
     </row>
     <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="6" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B517" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C517" s="11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D517" s="6"/>
       <c r="E517" s="6"/>
       <c r="F517" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G517" s="6"/>
       <c r="H517" s="6"/>
@@ -14591,18 +14495,18 @@
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B518" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C518" s="11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D518" s="6"/>
       <c r="E518" s="6"/>
       <c r="F518" s="6" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G518" s="6"/>
       <c r="H518" s="6"/>
@@ -14613,18 +14517,18 @@
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" s="6" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B519" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C519" s="11" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D519" s="6"/>
       <c r="E519" s="6"/>
       <c r="F519" s="6" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="G519" s="6"/>
       <c r="H519" s="6"/>
@@ -14635,18 +14539,18 @@
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A520" s="6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B520" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C520" s="11" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D520" s="6"/>
       <c r="E520" s="6"/>
       <c r="F520" s="6" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="G520" s="6"/>
       <c r="H520" s="6"/>
@@ -14657,18 +14561,18 @@
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A521" s="6" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B521" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D521" s="6"/>
       <c r="E521" s="6"/>
       <c r="F521" s="6" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="G521" s="6"/>
       <c r="H521" s="6"/>
@@ -14679,18 +14583,18 @@
     </row>
     <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" s="6" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B522" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D522" s="6"/>
       <c r="E522" s="6"/>
       <c r="F522" s="6" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="G522" s="6"/>
       <c r="H522" s="6"/>
@@ -14701,18 +14605,18 @@
     </row>
     <row r="523" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A523" s="6" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B523" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D523" s="6"/>
       <c r="E523" s="6"/>
       <c r="F523" s="6" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="G523" s="6"/>
       <c r="H523" s="6"/>
@@ -14723,18 +14627,18 @@
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" s="6" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B524" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C524" s="11" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="D524" s="6"/>
       <c r="E524" s="6"/>
       <c r="F524" s="6" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="G524" s="6"/>
       <c r="H524" s="6"/>
@@ -14745,18 +14649,18 @@
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" s="6" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B525" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D525" s="6"/>
       <c r="E525" s="6"/>
       <c r="F525" s="6" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="G525" s="6"/>
       <c r="H525" s="6"/>
@@ -14767,18 +14671,18 @@
     </row>
     <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="6" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B526" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D526" s="6"/>
       <c r="E526" s="6"/>
       <c r="F526" s="6" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="G526" s="6"/>
       <c r="H526" s="6"/>
@@ -14789,23 +14693,23 @@
     </row>
     <row r="527" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A527" s="6" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B527" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C527" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D527" s="6"/>
       <c r="E527" s="6"/>
       <c r="F527" s="6" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G527" s="6"/>
       <c r="H527" s="6"/>
       <c r="I527" s="11" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="J527" s="6" t="s">
         <v>13</v>
@@ -14873,18 +14777,18 @@
     </row>
     <row r="533" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A533" s="6" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B533" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D533" s="6"/>
       <c r="E533" s="6"/>
       <c r="F533" s="6" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="G533" s="6"/>
       <c r="H533" s="6"/>
@@ -14895,18 +14799,18 @@
     </row>
     <row r="534" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A534" s="6" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B534" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D534" s="6"/>
       <c r="E534" s="6"/>
       <c r="F534" s="6" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="G534" s="6"/>
       <c r="H534" s="6"/>
@@ -14917,18 +14821,18 @@
     </row>
     <row r="535" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A535" s="6" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B535" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C535" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D535" s="6"/>
       <c r="E535" s="6"/>
       <c r="F535" s="6" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="G535" s="6"/>
       <c r="H535" s="6"/>
@@ -14939,18 +14843,18 @@
     </row>
     <row r="536" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A536" s="6" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B536" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
       <c r="F536" s="6" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
@@ -14961,18 +14865,18 @@
     </row>
     <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" s="6" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B537" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C537" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D537" s="6"/>
       <c r="E537" s="6"/>
       <c r="F537" s="6" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G537" s="6"/>
       <c r="H537" s="6"/>
@@ -14983,18 +14887,18 @@
     </row>
     <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" s="6" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B538" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C538" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D538" s="6"/>
       <c r="E538" s="6"/>
       <c r="F538" s="6" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="G538" s="6"/>
       <c r="H538" s="6"/>
@@ -15005,18 +14909,18 @@
     </row>
     <row r="539" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A539" s="6" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B539" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C539" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D539" s="6"/>
       <c r="E539" s="6"/>
       <c r="F539" s="6" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="G539" s="6"/>
       <c r="H539" s="6"/>
@@ -15027,18 +14931,18 @@
     </row>
     <row r="540" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A540" s="6" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B540" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C540" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D540" s="6"/>
       <c r="E540" s="6"/>
       <c r="F540" s="6" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G540" s="6"/>
       <c r="H540" s="6"/>
@@ -15049,18 +14953,18 @@
     </row>
     <row r="541" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A541" s="6" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B541" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C541" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D541" s="6"/>
       <c r="E541" s="6"/>
       <c r="F541" s="6" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G541" s="6"/>
       <c r="H541" s="6"/>
@@ -15071,18 +14975,18 @@
     </row>
     <row r="542" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A542" s="6" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B542" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C542" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D542" s="6"/>
       <c r="E542" s="6"/>
       <c r="F542" s="6" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="G542" s="6"/>
       <c r="H542" s="6"/>
@@ -15093,18 +14997,18 @@
     </row>
     <row r="543" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A543" s="6" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B543" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C543" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D543" s="6"/>
       <c r="E543" s="6"/>
       <c r="F543" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="G543" s="6"/>
       <c r="H543" s="6"/>
@@ -15115,18 +15019,18 @@
     </row>
     <row r="544" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A544" s="6" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B544" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C544" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D544" s="6"/>
       <c r="E544" s="6"/>
       <c r="F544" s="6" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="G544" s="6"/>
       <c r="H544" s="6"/>
@@ -15137,18 +15041,18 @@
     </row>
     <row r="545" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A545" s="6" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B545" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
       <c r="F545" s="6" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
@@ -15159,18 +15063,18 @@
     </row>
     <row r="546" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B546" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C546" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
       <c r="F546" s="6" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
@@ -15181,18 +15085,18 @@
     </row>
     <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B547" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C547" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
       <c r="F547" s="6" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
@@ -15203,23 +15107,23 @@
     </row>
     <row r="548" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B548" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C548" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
       <c r="F548" s="11" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
       <c r="I548" s="11" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="J548" s="6" t="s">
         <v>13</v>
@@ -15251,18 +15155,18 @@
     </row>
     <row r="551" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A551" s="6" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B551" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C551" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
       <c r="F551" s="6" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
@@ -15273,18 +15177,18 @@
     </row>
     <row r="552" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A552" s="6" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B552" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C552" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
       <c r="F552" s="6" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
@@ -15295,18 +15199,18 @@
     </row>
     <row r="553" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A553" s="6" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B553" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
       <c r="F553" s="6" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
@@ -15346,13 +15250,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15360,10 +15264,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -15371,7 +15275,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -15382,7 +15286,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>94</v>
@@ -15393,21 +15297,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -15415,10 +15319,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -15426,10 +15330,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -15437,10 +15341,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -15448,10 +15352,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -15459,7 +15363,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>13</v>
@@ -15467,68 +15371,68 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -15538,21 +15442,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -15577,10 +15481,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>7</v>
@@ -15591,13 +15495,13 @@
         <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C2" t="s">
         <v>230</v>
       </c>
       <c r="D2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -15605,13 +15509,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -15619,13 +15523,13 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -15633,13 +15537,13 @@
         <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C5" t="s">
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -15647,13 +15551,13 @@
         <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C6" t="s">
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -15661,13 +15565,13 @@
         <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C7" t="s">
         <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -15675,27 +15579,27 @@
         <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C8" t="s">
         <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -15718,13 +15622,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>7</v>
@@ -15732,240 +15636,240 @@
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>230</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>230</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -15988,84 +15892,84 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>230</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>230</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
   </sheetData>

--- a/Blackwood_CFS_Master_Inventory_with_34P_and_CAFS24_Rescue_Unchanged.xlsx
+++ b/Blackwood_CFS_Master_Inventory_with_34P_and_CAFS24_Rescue_Unchanged.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\Blackwood CFS\App creation\V2 stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBB854D-21A9-4AFF-A790-3ABB95C5C19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Inventory" sheetId="1" r:id="rId1"/>
